--- a/5. Other/Danh sách số SIM BH-SX/SIM_Test BH-SX.xlsx
+++ b/5. Other/Danh sách số SIM BH-SX/SIM_Test BH-SX.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VNET\5. Other\Danh sách số SIM BH-SX\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9986250-F23C-43E9-8C34-BD6FEFF8F6A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44839A15-B890-4415-B8FC-362CA082EBFB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{68255EAF-D8EA-4C2C-BCF7-C24A5FBA6E37}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="48">
   <si>
     <t>Seri</t>
   </si>
@@ -167,6 +167,9 @@
   </si>
   <si>
     <t>Báo huỷ DV</t>
+  </si>
+  <si>
+    <t>Ghi chú</t>
   </si>
 </sst>
 </file>
@@ -298,7 +301,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -310,6 +313,12 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="49" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -331,12 +340,10 @@
     <xf numFmtId="49" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -659,9 +666,10 @@
     <col min="3" max="3" width="18" style="4" customWidth="1"/>
     <col min="4" max="4" width="18.5703125" style="4" customWidth="1"/>
     <col min="5" max="5" width="14.7109375" style="4" customWidth="1"/>
+    <col min="6" max="6" width="16.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>38</v>
       </c>
@@ -677,8 +685,11 @@
       <c r="E1" s="2" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F1" s="14" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="3">
         <v>1</v>
       </c>
@@ -691,11 +702,12 @@
       <c r="D2" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="E2" s="5" t="s">
+      <c r="E2" s="7" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F2" s="15"/>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="3">
         <v>2</v>
       </c>
@@ -705,12 +717,13 @@
       <c r="C3" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D3" s="6" t="s">
+      <c r="D3" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="E3" s="5"/>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E3" s="7"/>
+      <c r="F3" s="15"/>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="3">
         <v>3</v>
       </c>
@@ -720,10 +733,11 @@
       <c r="C4" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D4" s="7"/>
-      <c r="E4" s="5"/>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D4" s="9"/>
+      <c r="E4" s="7"/>
+      <c r="F4" s="15"/>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="3">
         <v>4</v>
       </c>
@@ -736,9 +750,10 @@
       <c r="D5" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="E5" s="5"/>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E5" s="7"/>
+      <c r="F5" s="15"/>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="3">
         <v>5</v>
       </c>
@@ -751,9 +766,10 @@
       <c r="D6" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="E6" s="5"/>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E6" s="7"/>
+      <c r="F6" s="15"/>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="3">
         <v>6</v>
       </c>
@@ -763,14 +779,15 @@
       <c r="C7" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="D7" s="6" t="s">
+      <c r="D7" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="E7" s="8" t="s">
+      <c r="E7" s="10" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F7" s="15"/>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="3">
         <v>7</v>
       </c>
@@ -780,10 +797,11 @@
       <c r="C8" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D8" s="11"/>
-      <c r="E8" s="9"/>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D8" s="13"/>
+      <c r="E8" s="11"/>
+      <c r="F8" s="15"/>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="3">
         <v>8</v>
       </c>
@@ -793,10 +811,11 @@
       <c r="C9" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D9" s="11"/>
-      <c r="E9" s="9"/>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D9" s="13"/>
+      <c r="E9" s="11"/>
+      <c r="F9" s="15"/>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="3">
         <v>9</v>
       </c>
@@ -806,10 +825,11 @@
       <c r="C10" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D10" s="7"/>
-      <c r="E10" s="9"/>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D10" s="9"/>
+      <c r="E10" s="11"/>
+      <c r="F10" s="15"/>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="3">
         <v>10</v>
       </c>
@@ -819,12 +839,13 @@
       <c r="C11" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D11" s="6" t="s">
+      <c r="D11" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="E11" s="9"/>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E11" s="11"/>
+      <c r="F11" s="15"/>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="3">
         <v>11</v>
       </c>
@@ -834,10 +855,11 @@
       <c r="C12" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D12" s="11"/>
-      <c r="E12" s="9"/>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D12" s="13"/>
+      <c r="E12" s="11"/>
+      <c r="F12" s="15"/>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="3">
         <v>12</v>
       </c>
@@ -847,10 +869,11 @@
       <c r="C13" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="D13" s="11"/>
-      <c r="E13" s="9"/>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D13" s="13"/>
+      <c r="E13" s="11"/>
+      <c r="F13" s="15"/>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="3">
         <v>13</v>
       </c>
@@ -860,10 +883,11 @@
       <c r="C14" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D14" s="7"/>
-      <c r="E14" s="9"/>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D14" s="9"/>
+      <c r="E14" s="11"/>
+      <c r="F14" s="15"/>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="3">
         <v>14</v>
       </c>
@@ -873,12 +897,13 @@
       <c r="C15" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D15" s="6" t="s">
+      <c r="D15" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="E15" s="9"/>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E15" s="11"/>
+      <c r="F15" s="15"/>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="3">
         <v>15</v>
       </c>
@@ -888,8 +913,9 @@
       <c r="C16" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D16" s="11"/>
-      <c r="E16" s="9"/>
+      <c r="D16" s="13"/>
+      <c r="E16" s="11"/>
+      <c r="F16" s="15"/>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="3">
@@ -901,8 +927,9 @@
       <c r="C17" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D17" s="11"/>
-      <c r="E17" s="9"/>
+      <c r="D17" s="13"/>
+      <c r="E17" s="11"/>
+      <c r="F17" s="15"/>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="3">
@@ -914,8 +941,9 @@
       <c r="C18" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D18" s="7"/>
-      <c r="E18" s="9"/>
+      <c r="D18" s="9"/>
+      <c r="E18" s="11"/>
+      <c r="F18" s="15"/>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="3">
@@ -927,10 +955,11 @@
       <c r="C19" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="D19" s="8" t="s">
+      <c r="D19" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="E19" s="9"/>
+      <c r="E19" s="11"/>
+      <c r="F19" s="15"/>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="3">
@@ -942,8 +971,9 @@
       <c r="C20" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D20" s="9"/>
-      <c r="E20" s="9"/>
+      <c r="D20" s="11"/>
+      <c r="E20" s="11"/>
+      <c r="F20" s="15"/>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="3">
@@ -955,8 +985,9 @@
       <c r="C21" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D21" s="9"/>
-      <c r="E21" s="9"/>
+      <c r="D21" s="11"/>
+      <c r="E21" s="11"/>
+      <c r="F21" s="15"/>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="3">
@@ -968,8 +999,9 @@
       <c r="C22" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="D22" s="9"/>
-      <c r="E22" s="9"/>
+      <c r="D22" s="11"/>
+      <c r="E22" s="11"/>
+      <c r="F22" s="15"/>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="3">
@@ -981,8 +1013,9 @@
       <c r="C23" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D23" s="9"/>
-      <c r="E23" s="9"/>
+      <c r="D23" s="11"/>
+      <c r="E23" s="11"/>
+      <c r="F23" s="15"/>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="3">
@@ -994,8 +1027,9 @@
       <c r="C24" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="D24" s="9"/>
-      <c r="E24" s="9"/>
+      <c r="D24" s="11"/>
+      <c r="E24" s="11"/>
+      <c r="F24" s="15"/>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="3">
@@ -1007,8 +1041,9 @@
       <c r="C25" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="D25" s="9"/>
-      <c r="E25" s="9"/>
+      <c r="D25" s="11"/>
+      <c r="E25" s="11"/>
+      <c r="F25" s="15"/>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="3">
@@ -1020,8 +1055,9 @@
       <c r="C26" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D26" s="9"/>
-      <c r="E26" s="9"/>
+      <c r="D26" s="11"/>
+      <c r="E26" s="11"/>
+      <c r="F26" s="15"/>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="3">
@@ -1033,8 +1069,9 @@
       <c r="C27" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D27" s="9"/>
-      <c r="E27" s="9"/>
+      <c r="D27" s="11"/>
+      <c r="E27" s="11"/>
+      <c r="F27" s="15"/>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="3">
@@ -1046,8 +1083,9 @@
       <c r="C28" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="D28" s="9"/>
-      <c r="E28" s="9"/>
+      <c r="D28" s="11"/>
+      <c r="E28" s="11"/>
+      <c r="F28" s="15"/>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="3">
@@ -1059,8 +1097,9 @@
       <c r="C29" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D29" s="9"/>
-      <c r="E29" s="9"/>
+      <c r="D29" s="11"/>
+      <c r="E29" s="11"/>
+      <c r="F29" s="15"/>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="3">
@@ -1072,8 +1111,9 @@
       <c r="C30" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="D30" s="9"/>
-      <c r="E30" s="9"/>
+      <c r="D30" s="11"/>
+      <c r="E30" s="11"/>
+      <c r="F30" s="15"/>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="3">
@@ -1085,26 +1125,27 @@
       <c r="C31" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="D31" s="9"/>
-      <c r="E31" s="9"/>
+      <c r="D31" s="11"/>
+      <c r="E31" s="11"/>
+      <c r="F31" s="15"/>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A32" s="12">
+      <c r="A32" s="5">
         <v>31</v>
       </c>
-      <c r="B32" s="13">
+      <c r="B32" s="6">
         <v>1173963065</v>
       </c>
-      <c r="C32" s="13" t="s">
+      <c r="C32" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="D32" s="9"/>
-      <c r="E32" s="9"/>
-      <c r="F32" t="s">
+      <c r="D32" s="11"/>
+      <c r="E32" s="11"/>
+      <c r="F32" s="15" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="3">
         <v>32</v>
       </c>
@@ -1114,10 +1155,11 @@
       <c r="C33" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="D33" s="9"/>
-      <c r="E33" s="9"/>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D33" s="11"/>
+      <c r="E33" s="11"/>
+      <c r="F33" s="15"/>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="3">
         <v>33</v>
       </c>
@@ -1127,10 +1169,11 @@
       <c r="C34" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="D34" s="9"/>
-      <c r="E34" s="9"/>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D34" s="11"/>
+      <c r="E34" s="11"/>
+      <c r="F34" s="15"/>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="3">
         <v>34</v>
       </c>
@@ -1140,10 +1183,11 @@
       <c r="C35" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D35" s="9"/>
-      <c r="E35" s="9"/>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D35" s="11"/>
+      <c r="E35" s="11"/>
+      <c r="F35" s="15"/>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="3">
         <v>35</v>
       </c>
@@ -1153,8 +1197,9 @@
       <c r="C36" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D36" s="10"/>
-      <c r="E36" s="10"/>
+      <c r="D36" s="12"/>
+      <c r="E36" s="12"/>
+      <c r="F36" s="15"/>
     </row>
   </sheetData>
   <mergeCells count="7">

--- a/5. Other/Danh sách số SIM BH-SX/SIM_Test BH-SX.xlsx
+++ b/5. Other/Danh sách số SIM BH-SX/SIM_Test BH-SX.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VNET\5. Other\Danh sách số SIM BH-SX\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44839A15-B890-4415-B8FC-362CA082EBFB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81FC1DE6-87C1-4EFE-9BBB-80339253CFCD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{68255EAF-D8EA-4C2C-BCF7-C24A5FBA6E37}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="49">
   <si>
     <t>Seri</t>
   </si>
@@ -170,6 +170,9 @@
   </si>
   <si>
     <t>Ghi chú</t>
+  </si>
+  <si>
+    <t>SIM không có dịch vụ</t>
   </si>
 </sst>
 </file>
@@ -319,6 +322,10 @@
     <xf numFmtId="49" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -340,10 +347,6 @@
     <xf numFmtId="49" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -666,7 +669,7 @@
     <col min="3" max="3" width="18" style="4" customWidth="1"/>
     <col min="4" max="4" width="18.5703125" style="4" customWidth="1"/>
     <col min="5" max="5" width="14.7109375" style="4" customWidth="1"/>
-    <col min="6" max="6" width="16.42578125" customWidth="1"/>
+    <col min="6" max="6" width="26" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -685,7 +688,7 @@
       <c r="E1" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="F1" s="14" t="s">
+      <c r="F1" s="7" t="s">
         <v>47</v>
       </c>
     </row>
@@ -702,10 +705,10 @@
       <c r="D2" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="E2" s="7" t="s">
+      <c r="E2" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="F2" s="15"/>
+      <c r="F2" s="8"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="3">
@@ -717,11 +720,11 @@
       <c r="C3" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D3" s="8" t="s">
+      <c r="D3" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="E3" s="7"/>
-      <c r="F3" s="15"/>
+      <c r="E3" s="9"/>
+      <c r="F3" s="8"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="3">
@@ -733,9 +736,9 @@
       <c r="C4" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D4" s="9"/>
-      <c r="E4" s="7"/>
-      <c r="F4" s="15"/>
+      <c r="D4" s="11"/>
+      <c r="E4" s="9"/>
+      <c r="F4" s="8"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="3">
@@ -750,8 +753,8 @@
       <c r="D5" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="E5" s="7"/>
-      <c r="F5" s="15"/>
+      <c r="E5" s="9"/>
+      <c r="F5" s="8"/>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="3">
@@ -766,8 +769,8 @@
       <c r="D6" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="E6" s="7"/>
-      <c r="F6" s="15"/>
+      <c r="E6" s="9"/>
+      <c r="F6" s="8"/>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="3">
@@ -779,13 +782,13 @@
       <c r="C7" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="D7" s="8" t="s">
+      <c r="D7" s="10" t="s">
         <v>41</v>
       </c>
-      <c r="E7" s="10" t="s">
+      <c r="E7" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="F7" s="15"/>
+      <c r="F7" s="8"/>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="3">
@@ -797,9 +800,9 @@
       <c r="C8" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D8" s="13"/>
-      <c r="E8" s="11"/>
-      <c r="F8" s="15"/>
+      <c r="D8" s="15"/>
+      <c r="E8" s="13"/>
+      <c r="F8" s="8"/>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="3">
@@ -811,9 +814,9 @@
       <c r="C9" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D9" s="13"/>
-      <c r="E9" s="11"/>
-      <c r="F9" s="15"/>
+      <c r="D9" s="15"/>
+      <c r="E9" s="13"/>
+      <c r="F9" s="8"/>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="3">
@@ -825,9 +828,9 @@
       <c r="C10" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D10" s="9"/>
-      <c r="E10" s="11"/>
-      <c r="F10" s="15"/>
+      <c r="D10" s="11"/>
+      <c r="E10" s="13"/>
+      <c r="F10" s="8"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="3">
@@ -839,11 +842,11 @@
       <c r="C11" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D11" s="8" t="s">
+      <c r="D11" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="E11" s="11"/>
-      <c r="F11" s="15"/>
+      <c r="E11" s="13"/>
+      <c r="F11" s="8"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="3">
@@ -855,9 +858,9 @@
       <c r="C12" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D12" s="13"/>
-      <c r="E12" s="11"/>
-      <c r="F12" s="15"/>
+      <c r="D12" s="15"/>
+      <c r="E12" s="13"/>
+      <c r="F12" s="8"/>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="3">
@@ -869,9 +872,9 @@
       <c r="C13" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="D13" s="13"/>
-      <c r="E13" s="11"/>
-      <c r="F13" s="15"/>
+      <c r="D13" s="15"/>
+      <c r="E13" s="13"/>
+      <c r="F13" s="8"/>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="3">
@@ -883,9 +886,9 @@
       <c r="C14" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D14" s="9"/>
-      <c r="E14" s="11"/>
-      <c r="F14" s="15"/>
+      <c r="D14" s="11"/>
+      <c r="E14" s="13"/>
+      <c r="F14" s="8"/>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="3">
@@ -897,11 +900,11 @@
       <c r="C15" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D15" s="8" t="s">
+      <c r="D15" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="E15" s="11"/>
-      <c r="F15" s="15"/>
+      <c r="E15" s="13"/>
+      <c r="F15" s="8"/>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="3">
@@ -913,9 +916,9 @@
       <c r="C16" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D16" s="13"/>
-      <c r="E16" s="11"/>
-      <c r="F16" s="15"/>
+      <c r="D16" s="15"/>
+      <c r="E16" s="13"/>
+      <c r="F16" s="8"/>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="3">
@@ -927,9 +930,9 @@
       <c r="C17" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D17" s="13"/>
-      <c r="E17" s="11"/>
-      <c r="F17" s="15"/>
+      <c r="D17" s="15"/>
+      <c r="E17" s="13"/>
+      <c r="F17" s="8"/>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="3">
@@ -941,9 +944,9 @@
       <c r="C18" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D18" s="9"/>
-      <c r="E18" s="11"/>
-      <c r="F18" s="15"/>
+      <c r="D18" s="11"/>
+      <c r="E18" s="13"/>
+      <c r="F18" s="8"/>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="3">
@@ -955,11 +958,11 @@
       <c r="C19" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="D19" s="10" t="s">
+      <c r="D19" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="E19" s="11"/>
-      <c r="F19" s="15"/>
+      <c r="E19" s="13"/>
+      <c r="F19" s="8"/>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="3">
@@ -971,9 +974,9 @@
       <c r="C20" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D20" s="11"/>
-      <c r="E20" s="11"/>
-      <c r="F20" s="15"/>
+      <c r="D20" s="13"/>
+      <c r="E20" s="13"/>
+      <c r="F20" s="8"/>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="3">
@@ -985,9 +988,9 @@
       <c r="C21" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D21" s="11"/>
-      <c r="E21" s="11"/>
-      <c r="F21" s="15"/>
+      <c r="D21" s="13"/>
+      <c r="E21" s="13"/>
+      <c r="F21" s="8"/>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="3">
@@ -999,23 +1002,25 @@
       <c r="C22" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="D22" s="11"/>
-      <c r="E22" s="11"/>
-      <c r="F22" s="15"/>
+      <c r="D22" s="13"/>
+      <c r="E22" s="13"/>
+      <c r="F22" s="8"/>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A23" s="3">
+      <c r="A23" s="5">
         <v>22</v>
       </c>
-      <c r="B23" s="1">
+      <c r="B23" s="6">
         <v>1173963056</v>
       </c>
-      <c r="C23" s="1" t="s">
+      <c r="C23" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="D23" s="11"/>
-      <c r="E23" s="11"/>
-      <c r="F23" s="15"/>
+      <c r="D23" s="13"/>
+      <c r="E23" s="13"/>
+      <c r="F23" s="8" t="s">
+        <v>48</v>
+      </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="3">
@@ -1027,9 +1032,9 @@
       <c r="C24" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="D24" s="11"/>
-      <c r="E24" s="11"/>
-      <c r="F24" s="15"/>
+      <c r="D24" s="13"/>
+      <c r="E24" s="13"/>
+      <c r="F24" s="8"/>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="3">
@@ -1041,9 +1046,9 @@
       <c r="C25" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="D25" s="11"/>
-      <c r="E25" s="11"/>
-      <c r="F25" s="15"/>
+      <c r="D25" s="13"/>
+      <c r="E25" s="13"/>
+      <c r="F25" s="8"/>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="3">
@@ -1055,9 +1060,9 @@
       <c r="C26" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D26" s="11"/>
-      <c r="E26" s="11"/>
-      <c r="F26" s="15"/>
+      <c r="D26" s="13"/>
+      <c r="E26" s="13"/>
+      <c r="F26" s="8"/>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="3">
@@ -1069,9 +1074,9 @@
       <c r="C27" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D27" s="11"/>
-      <c r="E27" s="11"/>
-      <c r="F27" s="15"/>
+      <c r="D27" s="13"/>
+      <c r="E27" s="13"/>
+      <c r="F27" s="8"/>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="3">
@@ -1083,9 +1088,9 @@
       <c r="C28" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="D28" s="11"/>
-      <c r="E28" s="11"/>
-      <c r="F28" s="15"/>
+      <c r="D28" s="13"/>
+      <c r="E28" s="13"/>
+      <c r="F28" s="8"/>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="3">
@@ -1097,9 +1102,9 @@
       <c r="C29" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D29" s="11"/>
-      <c r="E29" s="11"/>
-      <c r="F29" s="15"/>
+      <c r="D29" s="13"/>
+      <c r="E29" s="13"/>
+      <c r="F29" s="8"/>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="3">
@@ -1111,9 +1116,9 @@
       <c r="C30" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="D30" s="11"/>
-      <c r="E30" s="11"/>
-      <c r="F30" s="15"/>
+      <c r="D30" s="13"/>
+      <c r="E30" s="13"/>
+      <c r="F30" s="8"/>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="3">
@@ -1125,9 +1130,9 @@
       <c r="C31" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="D31" s="11"/>
-      <c r="E31" s="11"/>
-      <c r="F31" s="15"/>
+      <c r="D31" s="13"/>
+      <c r="E31" s="13"/>
+      <c r="F31" s="8"/>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="5">
@@ -1139,9 +1144,9 @@
       <c r="C32" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="D32" s="11"/>
-      <c r="E32" s="11"/>
-      <c r="F32" s="15" t="s">
+      <c r="D32" s="13"/>
+      <c r="E32" s="13"/>
+      <c r="F32" s="8" t="s">
         <v>46</v>
       </c>
     </row>
@@ -1155,9 +1160,9 @@
       <c r="C33" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="D33" s="11"/>
-      <c r="E33" s="11"/>
-      <c r="F33" s="15"/>
+      <c r="D33" s="13"/>
+      <c r="E33" s="13"/>
+      <c r="F33" s="8"/>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="3">
@@ -1169,9 +1174,9 @@
       <c r="C34" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="D34" s="11"/>
-      <c r="E34" s="11"/>
-      <c r="F34" s="15"/>
+      <c r="D34" s="13"/>
+      <c r="E34" s="13"/>
+      <c r="F34" s="8"/>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="3">
@@ -1183,9 +1188,9 @@
       <c r="C35" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D35" s="11"/>
-      <c r="E35" s="11"/>
-      <c r="F35" s="15"/>
+      <c r="D35" s="13"/>
+      <c r="E35" s="13"/>
+      <c r="F35" s="8"/>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="3">
@@ -1197,9 +1202,9 @@
       <c r="C36" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D36" s="12"/>
-      <c r="E36" s="12"/>
-      <c r="F36" s="15"/>
+      <c r="D36" s="14"/>
+      <c r="E36" s="14"/>
+      <c r="F36" s="8"/>
     </row>
   </sheetData>
   <mergeCells count="7">

--- a/5. Other/Danh sách số SIM BH-SX/SIM_Test BH-SX.xlsx
+++ b/5. Other/Danh sách số SIM BH-SX/SIM_Test BH-SX.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VNET\5. Other\Danh sách số SIM BH-SX\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81FC1DE6-87C1-4EFE-9BBB-80339253CFCD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5C96FBC-928F-4041-935D-36951D81E381}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{68255EAF-D8EA-4C2C-BCF7-C24A5FBA6E37}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="50">
   <si>
     <t>Seri</t>
   </si>
@@ -173,6 +173,9 @@
   </si>
   <si>
     <t>SIM không có dịch vụ</t>
+  </si>
+  <si>
+    <t>SIM lỗi</t>
   </si>
 </sst>
 </file>
@@ -220,7 +223,7 @@
       <family val="1"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -236,6 +239,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFF0000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -304,7 +313,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -346,6 +355,15 @@
     </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -760,7 +778,7 @@
       <c r="A6" s="3">
         <v>5</v>
       </c>
-      <c r="B6" s="1">
+      <c r="B6" s="18">
         <v>1174966078</v>
       </c>
       <c r="C6" s="1" t="s">
@@ -952,7 +970,7 @@
       <c r="A19" s="3">
         <v>18</v>
       </c>
-      <c r="B19" s="1">
+      <c r="B19" s="18">
         <v>1173963052</v>
       </c>
       <c r="C19" s="1" t="s">
@@ -968,7 +986,7 @@
       <c r="A20" s="3">
         <v>19</v>
       </c>
-      <c r="B20" s="1">
+      <c r="B20" s="18">
         <v>1173963053</v>
       </c>
       <c r="C20" s="1" t="s">
@@ -982,7 +1000,7 @@
       <c r="A21" s="3">
         <v>20</v>
       </c>
-      <c r="B21" s="1">
+      <c r="B21" s="18">
         <v>1173963054</v>
       </c>
       <c r="C21" s="1" t="s">
@@ -996,7 +1014,7 @@
       <c r="A22" s="3">
         <v>21</v>
       </c>
-      <c r="B22" s="1">
+      <c r="B22" s="18">
         <v>1173963055</v>
       </c>
       <c r="C22" s="1" t="s">
@@ -1026,7 +1044,7 @@
       <c r="A24" s="3">
         <v>23</v>
       </c>
-      <c r="B24" s="1">
+      <c r="B24" s="18">
         <v>1173963057</v>
       </c>
       <c r="C24" s="1" t="s">
@@ -1040,7 +1058,7 @@
       <c r="A25" s="3">
         <v>24</v>
       </c>
-      <c r="B25" s="1">
+      <c r="B25" s="18">
         <v>1173963058</v>
       </c>
       <c r="C25" s="1" t="s">
@@ -1054,7 +1072,7 @@
       <c r="A26" s="3">
         <v>25</v>
       </c>
-      <c r="B26" s="1">
+      <c r="B26" s="18">
         <v>1173963059</v>
       </c>
       <c r="C26" s="1" t="s">
@@ -1068,7 +1086,7 @@
       <c r="A27" s="3">
         <v>26</v>
       </c>
-      <c r="B27" s="1">
+      <c r="B27" s="18">
         <v>1173963060</v>
       </c>
       <c r="C27" s="1" t="s">
@@ -1079,24 +1097,26 @@
       <c r="F27" s="8"/>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A28" s="3">
+      <c r="A28" s="16">
         <v>27</v>
       </c>
-      <c r="B28" s="1">
+      <c r="B28" s="17">
         <v>1173963061</v>
       </c>
-      <c r="C28" s="1" t="s">
+      <c r="C28" s="17" t="s">
         <v>29</v>
       </c>
       <c r="D28" s="13"/>
       <c r="E28" s="13"/>
-      <c r="F28" s="8"/>
+      <c r="F28" s="8" t="s">
+        <v>49</v>
+      </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="3">
         <v>28</v>
       </c>
-      <c r="B29" s="1">
+      <c r="B29" s="18">
         <v>1173963062</v>
       </c>
       <c r="C29" s="1" t="s">
@@ -1110,7 +1130,7 @@
       <c r="A30" s="3">
         <v>29</v>
       </c>
-      <c r="B30" s="1">
+      <c r="B30" s="18">
         <v>1173963063</v>
       </c>
       <c r="C30" s="1" t="s">
@@ -1124,7 +1144,7 @@
       <c r="A31" s="3">
         <v>30</v>
       </c>
-      <c r="B31" s="1">
+      <c r="B31" s="18">
         <v>1173963064</v>
       </c>
       <c r="C31" s="1" t="s">
@@ -1154,7 +1174,7 @@
       <c r="A33" s="3">
         <v>32</v>
       </c>
-      <c r="B33" s="1">
+      <c r="B33" s="18">
         <v>1173963066</v>
       </c>
       <c r="C33" s="1" t="s">
@@ -1168,7 +1188,7 @@
       <c r="A34" s="3">
         <v>33</v>
       </c>
-      <c r="B34" s="1">
+      <c r="B34" s="18">
         <v>1173963067</v>
       </c>
       <c r="C34" s="1" t="s">
@@ -1182,7 +1202,7 @@
       <c r="A35" s="3">
         <v>34</v>
       </c>
-      <c r="B35" s="1">
+      <c r="B35" s="18">
         <v>1170534788</v>
       </c>
       <c r="C35" s="1" t="s">
@@ -1196,7 +1216,7 @@
       <c r="A36" s="3">
         <v>35</v>
       </c>
-      <c r="B36" s="1">
+      <c r="B36" s="18">
         <v>1170534789</v>
       </c>
       <c r="C36" s="1" t="s">

--- a/5. Other/Danh sách số SIM BH-SX/SIM_Test BH-SX.xlsx
+++ b/5. Other/Danh sách số SIM BH-SX/SIM_Test BH-SX.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VNET\5. Other\Danh sách số SIM BH-SX\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5C96FBC-928F-4041-935D-36951D81E381}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5805C281-B3CD-48EC-AF03-77CD1580D596}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{68255EAF-D8EA-4C2C-BCF7-C24A5FBA6E37}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="50">
   <si>
     <t>Seri</t>
   </si>
@@ -335,6 +335,15 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -355,15 +364,6 @@
     </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -723,7 +723,7 @@
       <c r="D2" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="E2" s="9" t="s">
+      <c r="E2" s="12" t="s">
         <v>40</v>
       </c>
       <c r="F2" s="8"/>
@@ -738,10 +738,10 @@
       <c r="C3" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D3" s="10" t="s">
+      <c r="D3" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="E3" s="9"/>
+      <c r="E3" s="12"/>
       <c r="F3" s="8"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -754,8 +754,8 @@
       <c r="C4" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D4" s="11"/>
-      <c r="E4" s="9"/>
+      <c r="D4" s="14"/>
+      <c r="E4" s="12"/>
       <c r="F4" s="8"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
@@ -771,14 +771,14 @@
       <c r="D5" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="E5" s="9"/>
+      <c r="E5" s="12"/>
       <c r="F5" s="8"/>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="3">
         <v>5</v>
       </c>
-      <c r="B6" s="18">
+      <c r="B6" s="11">
         <v>1174966078</v>
       </c>
       <c r="C6" s="1" t="s">
@@ -787,7 +787,7 @@
       <c r="D6" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="E6" s="9"/>
+      <c r="E6" s="12"/>
       <c r="F6" s="8"/>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -800,10 +800,10 @@
       <c r="C7" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="D7" s="10" t="s">
+      <c r="D7" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="E7" s="12" t="s">
+      <c r="E7" s="15" t="s">
         <v>45</v>
       </c>
       <c r="F7" s="8"/>
@@ -818,9 +818,11 @@
       <c r="C8" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D8" s="15"/>
-      <c r="E8" s="13"/>
-      <c r="F8" s="8"/>
+      <c r="D8" s="18"/>
+      <c r="E8" s="16"/>
+      <c r="F8" s="8" t="s">
+        <v>49</v>
+      </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="3">
@@ -832,8 +834,8 @@
       <c r="C9" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D9" s="15"/>
-      <c r="E9" s="13"/>
+      <c r="D9" s="18"/>
+      <c r="E9" s="16"/>
       <c r="F9" s="8"/>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
@@ -846,8 +848,8 @@
       <c r="C10" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D10" s="11"/>
-      <c r="E10" s="13"/>
+      <c r="D10" s="14"/>
+      <c r="E10" s="16"/>
       <c r="F10" s="8"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
@@ -860,10 +862,10 @@
       <c r="C11" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D11" s="10" t="s">
+      <c r="D11" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="E11" s="13"/>
+      <c r="E11" s="16"/>
       <c r="F11" s="8"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
@@ -876,8 +878,8 @@
       <c r="C12" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D12" s="15"/>
-      <c r="E12" s="13"/>
+      <c r="D12" s="18"/>
+      <c r="E12" s="16"/>
       <c r="F12" s="8"/>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
@@ -890,8 +892,8 @@
       <c r="C13" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="D13" s="15"/>
-      <c r="E13" s="13"/>
+      <c r="D13" s="18"/>
+      <c r="E13" s="16"/>
       <c r="F13" s="8"/>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
@@ -904,8 +906,8 @@
       <c r="C14" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D14" s="11"/>
-      <c r="E14" s="13"/>
+      <c r="D14" s="14"/>
+      <c r="E14" s="16"/>
       <c r="F14" s="8"/>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
@@ -918,10 +920,10 @@
       <c r="C15" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D15" s="10" t="s">
+      <c r="D15" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="E15" s="13"/>
+      <c r="E15" s="16"/>
       <c r="F15" s="8"/>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
@@ -934,8 +936,8 @@
       <c r="C16" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D16" s="15"/>
-      <c r="E16" s="13"/>
+      <c r="D16" s="18"/>
+      <c r="E16" s="16"/>
       <c r="F16" s="8"/>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
@@ -948,8 +950,8 @@
       <c r="C17" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D17" s="15"/>
-      <c r="E17" s="13"/>
+      <c r="D17" s="18"/>
+      <c r="E17" s="16"/>
       <c r="F17" s="8"/>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
@@ -962,66 +964,66 @@
       <c r="C18" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D18" s="11"/>
-      <c r="E18" s="13"/>
+      <c r="D18" s="14"/>
+      <c r="E18" s="16"/>
       <c r="F18" s="8"/>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="3">
         <v>18</v>
       </c>
-      <c r="B19" s="18">
+      <c r="B19" s="11">
         <v>1173963052</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="D19" s="12" t="s">
+      <c r="D19" s="15" t="s">
         <v>44</v>
       </c>
-      <c r="E19" s="13"/>
+      <c r="E19" s="16"/>
       <c r="F19" s="8"/>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="3">
         <v>19</v>
       </c>
-      <c r="B20" s="18">
+      <c r="B20" s="11">
         <v>1173963053</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D20" s="13"/>
-      <c r="E20" s="13"/>
+      <c r="D20" s="16"/>
+      <c r="E20" s="16"/>
       <c r="F20" s="8"/>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="3">
         <v>20</v>
       </c>
-      <c r="B21" s="18">
+      <c r="B21" s="11">
         <v>1173963054</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D21" s="13"/>
-      <c r="E21" s="13"/>
+      <c r="D21" s="16"/>
+      <c r="E21" s="16"/>
       <c r="F21" s="8"/>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="3">
         <v>21</v>
       </c>
-      <c r="B22" s="18">
+      <c r="B22" s="11">
         <v>1173963055</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="D22" s="13"/>
-      <c r="E22" s="13"/>
+      <c r="D22" s="16"/>
+      <c r="E22" s="16"/>
       <c r="F22" s="8"/>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
@@ -1034,8 +1036,8 @@
       <c r="C23" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="D23" s="13"/>
-      <c r="E23" s="13"/>
+      <c r="D23" s="16"/>
+      <c r="E23" s="16"/>
       <c r="F23" s="8" t="s">
         <v>48</v>
       </c>
@@ -1044,70 +1046,70 @@
       <c r="A24" s="3">
         <v>23</v>
       </c>
-      <c r="B24" s="18">
+      <c r="B24" s="11">
         <v>1173963057</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="D24" s="13"/>
-      <c r="E24" s="13"/>
+      <c r="D24" s="16"/>
+      <c r="E24" s="16"/>
       <c r="F24" s="8"/>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="3">
         <v>24</v>
       </c>
-      <c r="B25" s="18">
+      <c r="B25" s="11">
         <v>1173963058</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="D25" s="13"/>
-      <c r="E25" s="13"/>
+      <c r="D25" s="16"/>
+      <c r="E25" s="16"/>
       <c r="F25" s="8"/>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="3">
         <v>25</v>
       </c>
-      <c r="B26" s="18">
+      <c r="B26" s="11">
         <v>1173963059</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D26" s="13"/>
-      <c r="E26" s="13"/>
+      <c r="D26" s="16"/>
+      <c r="E26" s="16"/>
       <c r="F26" s="8"/>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="3">
         <v>26</v>
       </c>
-      <c r="B27" s="18">
+      <c r="B27" s="11">
         <v>1173963060</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D27" s="13"/>
-      <c r="E27" s="13"/>
+      <c r="D27" s="16"/>
+      <c r="E27" s="16"/>
       <c r="F27" s="8"/>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A28" s="16">
+      <c r="A28" s="9">
         <v>27</v>
       </c>
-      <c r="B28" s="17">
+      <c r="B28" s="10">
         <v>1173963061</v>
       </c>
-      <c r="C28" s="17" t="s">
+      <c r="C28" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="D28" s="13"/>
-      <c r="E28" s="13"/>
+      <c r="D28" s="16"/>
+      <c r="E28" s="16"/>
       <c r="F28" s="8" t="s">
         <v>49</v>
       </c>
@@ -1116,42 +1118,42 @@
       <c r="A29" s="3">
         <v>28</v>
       </c>
-      <c r="B29" s="18">
+      <c r="B29" s="11">
         <v>1173963062</v>
       </c>
       <c r="C29" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D29" s="13"/>
-      <c r="E29" s="13"/>
+      <c r="D29" s="16"/>
+      <c r="E29" s="16"/>
       <c r="F29" s="8"/>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="3">
         <v>29</v>
       </c>
-      <c r="B30" s="18">
+      <c r="B30" s="11">
         <v>1173963063</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="D30" s="13"/>
-      <c r="E30" s="13"/>
+      <c r="D30" s="16"/>
+      <c r="E30" s="16"/>
       <c r="F30" s="8"/>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="3">
         <v>30</v>
       </c>
-      <c r="B31" s="18">
+      <c r="B31" s="11">
         <v>1173963064</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="D31" s="13"/>
-      <c r="E31" s="13"/>
+      <c r="D31" s="16"/>
+      <c r="E31" s="16"/>
       <c r="F31" s="8"/>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
@@ -1164,8 +1166,8 @@
       <c r="C32" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="D32" s="13"/>
-      <c r="E32" s="13"/>
+      <c r="D32" s="16"/>
+      <c r="E32" s="16"/>
       <c r="F32" s="8" t="s">
         <v>46</v>
       </c>
@@ -1174,56 +1176,56 @@
       <c r="A33" s="3">
         <v>32</v>
       </c>
-      <c r="B33" s="18">
+      <c r="B33" s="11">
         <v>1173963066</v>
       </c>
       <c r="C33" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="D33" s="13"/>
-      <c r="E33" s="13"/>
+      <c r="D33" s="16"/>
+      <c r="E33" s="16"/>
       <c r="F33" s="8"/>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="3">
         <v>33</v>
       </c>
-      <c r="B34" s="18">
+      <c r="B34" s="11">
         <v>1173963067</v>
       </c>
       <c r="C34" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="D34" s="13"/>
-      <c r="E34" s="13"/>
+      <c r="D34" s="16"/>
+      <c r="E34" s="16"/>
       <c r="F34" s="8"/>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="3">
         <v>34</v>
       </c>
-      <c r="B35" s="18">
+      <c r="B35" s="11">
         <v>1170534788</v>
       </c>
       <c r="C35" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D35" s="13"/>
-      <c r="E35" s="13"/>
+      <c r="D35" s="16"/>
+      <c r="E35" s="16"/>
       <c r="F35" s="8"/>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="3">
         <v>35</v>
       </c>
-      <c r="B36" s="18">
+      <c r="B36" s="11">
         <v>1170534789</v>
       </c>
       <c r="C36" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D36" s="14"/>
-      <c r="E36" s="14"/>
+      <c r="D36" s="17"/>
+      <c r="E36" s="17"/>
       <c r="F36" s="8"/>
     </row>
   </sheetData>

--- a/5. Other/Danh sách số SIM BH-SX/SIM_Test BH-SX.xlsx
+++ b/5. Other/Danh sách số SIM BH-SX/SIM_Test BH-SX.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VNET\5. Other\Danh sách số SIM BH-SX\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5805C281-B3CD-48EC-AF03-77CD1580D596}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C499265-1F56-4B65-95E4-C8753070B872}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{68255EAF-D8EA-4C2C-BCF7-C24A5FBA6E37}"/>
   </bookViews>

--- a/5. Other/Danh sách số SIM BH-SX/SIM_Test BH-SX.xlsx
+++ b/5. Other/Danh sách số SIM BH-SX/SIM_Test BH-SX.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VNET\5. Other\Danh sách số SIM BH-SX\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C499265-1F56-4B65-95E4-C8753070B872}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB7F216F-19E8-4CB5-A87F-CD97144C120A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{68255EAF-D8EA-4C2C-BCF7-C24A5FBA6E37}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="50">
   <si>
     <t>Seri</t>
   </si>
@@ -160,15 +160,9 @@
     <t>Quang</t>
   </si>
   <si>
-    <t>Đạt</t>
-  </si>
-  <si>
     <t>Test định vị</t>
   </si>
   <si>
-    <t>Báo huỷ DV</t>
-  </si>
-  <si>
     <t>Ghi chú</t>
   </si>
   <si>
@@ -176,6 +170,12 @@
   </si>
   <si>
     <t>SIM lỗi</t>
+  </si>
+  <si>
+    <t>Báo huỷ DV, mất phôi</t>
+  </si>
+  <si>
+    <t>SIM lỗi, mất phôi</t>
   </si>
 </sst>
 </file>
@@ -223,7 +223,7 @@
       <family val="1"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -245,6 +245,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -318,9 +324,6 @@
     <xf numFmtId="49" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -331,9 +334,6 @@
     <xf numFmtId="49" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -363,6 +363,12 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -682,36 +688,36 @@
   <dimension ref="A1:F36"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.140625" style="4" customWidth="1"/>
-    <col min="2" max="2" width="15.85546875" style="4" customWidth="1"/>
-    <col min="3" max="3" width="18" style="4" customWidth="1"/>
-    <col min="4" max="4" width="18.5703125" style="4" customWidth="1"/>
-    <col min="5" max="5" width="14.7109375" style="4" customWidth="1"/>
+    <col min="1" max="1" width="5.140625" style="3" customWidth="1"/>
+    <col min="2" max="2" width="15.85546875" style="3" customWidth="1"/>
+    <col min="3" max="3" width="18" style="3" customWidth="1"/>
+    <col min="4" max="4" width="18.5703125" style="3" customWidth="1"/>
+    <col min="5" max="5" width="14.7109375" style="3" customWidth="1"/>
     <col min="6" max="6" width="26" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="17" t="s">
         <v>38</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="17" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="17" t="s">
         <v>39</v>
       </c>
-      <c r="F1" s="7" t="s">
-        <v>47</v>
+      <c r="F1" s="18" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="3">
+      <c r="A2" s="2">
         <v>1</v>
       </c>
       <c r="B2" s="1">
@@ -720,16 +726,16 @@
       <c r="C2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="D2" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="E2" s="12" t="s">
+      <c r="E2" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="F2" s="8"/>
+      <c r="F2" s="6"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="3">
+      <c r="A3" s="2">
         <v>2</v>
       </c>
       <c r="B3" s="1">
@@ -738,14 +744,14 @@
       <c r="C3" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D3" s="13" t="s">
+      <c r="D3" s="11" t="s">
         <v>42</v>
       </c>
-      <c r="E3" s="12"/>
-      <c r="F3" s="8"/>
+      <c r="E3" s="10"/>
+      <c r="F3" s="6"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="3">
+      <c r="A4" s="2">
         <v>3</v>
       </c>
       <c r="B4" s="1">
@@ -754,12 +760,12 @@
       <c r="C4" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D4" s="14"/>
-      <c r="E4" s="12"/>
-      <c r="F4" s="8"/>
+      <c r="D4" s="12"/>
+      <c r="E4" s="10"/>
+      <c r="F4" s="6"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="3">
+      <c r="A5" s="2">
         <v>4</v>
       </c>
       <c r="B5" s="1">
@@ -768,30 +774,28 @@
       <c r="C5" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D5" s="3" t="s">
+      <c r="D5" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="E5" s="12"/>
-      <c r="F5" s="8"/>
+      <c r="E5" s="10"/>
+      <c r="F5" s="6"/>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="3">
+      <c r="A6" s="2">
         <v>5</v>
       </c>
-      <c r="B6" s="11">
+      <c r="B6" s="9">
         <v>1174966078</v>
       </c>
-      <c r="C6" s="1" t="s">
+      <c r="C6" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="D6" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="E6" s="12"/>
-      <c r="F6" s="8"/>
+      <c r="D6" s="15"/>
+      <c r="E6" s="10"/>
+      <c r="F6" s="6"/>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="3">
+      <c r="A7" s="2">
         <v>6</v>
       </c>
       <c r="B7" s="1">
@@ -800,16 +804,16 @@
       <c r="C7" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="D7" s="13" t="s">
+      <c r="D7" s="11" t="s">
         <v>41</v>
       </c>
-      <c r="E7" s="15" t="s">
-        <v>45</v>
-      </c>
-      <c r="F7" s="8"/>
+      <c r="E7" s="13" t="s">
+        <v>44</v>
+      </c>
+      <c r="F7" s="6"/>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="3">
+      <c r="A8" s="2">
         <v>7</v>
       </c>
       <c r="B8" s="1">
@@ -818,14 +822,14 @@
       <c r="C8" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D8" s="18"/>
-      <c r="E8" s="16"/>
-      <c r="F8" s="8" t="s">
-        <v>49</v>
+      <c r="D8" s="16"/>
+      <c r="E8" s="14"/>
+      <c r="F8" s="6" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="3">
+      <c r="A9" s="2">
         <v>8</v>
       </c>
       <c r="B9" s="1">
@@ -834,12 +838,12 @@
       <c r="C9" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D9" s="18"/>
-      <c r="E9" s="16"/>
-      <c r="F9" s="8"/>
+      <c r="D9" s="16"/>
+      <c r="E9" s="14"/>
+      <c r="F9" s="6"/>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="3">
+      <c r="A10" s="2">
         <v>9</v>
       </c>
       <c r="B10" s="1">
@@ -848,12 +852,12 @@
       <c r="C10" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D10" s="14"/>
-      <c r="E10" s="16"/>
-      <c r="F10" s="8"/>
+      <c r="D10" s="12"/>
+      <c r="E10" s="14"/>
+      <c r="F10" s="6"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="3">
+      <c r="A11" s="2">
         <v>10</v>
       </c>
       <c r="B11" s="1">
@@ -862,14 +866,14 @@
       <c r="C11" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D11" s="13" t="s">
+      <c r="D11" s="11" t="s">
         <v>42</v>
       </c>
-      <c r="E11" s="16"/>
-      <c r="F11" s="8"/>
+      <c r="E11" s="14"/>
+      <c r="F11" s="6"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="3">
+      <c r="A12" s="2">
         <v>11</v>
       </c>
       <c r="B12" s="1">
@@ -878,12 +882,12 @@
       <c r="C12" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D12" s="18"/>
-      <c r="E12" s="16"/>
-      <c r="F12" s="8"/>
+      <c r="D12" s="16"/>
+      <c r="E12" s="14"/>
+      <c r="F12" s="6"/>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="3">
+      <c r="A13" s="2">
         <v>12</v>
       </c>
       <c r="B13" s="1">
@@ -892,12 +896,12 @@
       <c r="C13" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="D13" s="18"/>
-      <c r="E13" s="16"/>
-      <c r="F13" s="8"/>
+      <c r="D13" s="16"/>
+      <c r="E13" s="14"/>
+      <c r="F13" s="6"/>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" s="3">
+      <c r="A14" s="2">
         <v>13</v>
       </c>
       <c r="B14" s="1">
@@ -906,12 +910,12 @@
       <c r="C14" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D14" s="14"/>
-      <c r="E14" s="16"/>
-      <c r="F14" s="8"/>
+      <c r="D14" s="12"/>
+      <c r="E14" s="14"/>
+      <c r="F14" s="6"/>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" s="3">
+      <c r="A15" s="2">
         <v>14</v>
       </c>
       <c r="B15" s="1">
@@ -923,11 +927,11 @@
       <c r="D15" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="E15" s="16"/>
-      <c r="F15" s="8"/>
+      <c r="E15" s="14"/>
+      <c r="F15" s="6"/>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" s="3">
+      <c r="A16" s="2">
         <v>15</v>
       </c>
       <c r="B16" s="1">
@@ -936,12 +940,12 @@
       <c r="C16" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D16" s="18"/>
-      <c r="E16" s="16"/>
-      <c r="F16" s="8"/>
+      <c r="D16" s="14"/>
+      <c r="E16" s="14"/>
+      <c r="F16" s="6"/>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" s="3">
+      <c r="A17" s="2">
         <v>16</v>
       </c>
       <c r="B17" s="1">
@@ -950,12 +954,12 @@
       <c r="C17" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D17" s="18"/>
-      <c r="E17" s="16"/>
-      <c r="F17" s="8"/>
+      <c r="D17" s="14"/>
+      <c r="E17" s="14"/>
+      <c r="F17" s="6"/>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A18" s="3">
+      <c r="A18" s="2">
         <v>17</v>
       </c>
       <c r="B18" s="1">
@@ -965,268 +969,266 @@
         <v>19</v>
       </c>
       <c r="D18" s="14"/>
-      <c r="E18" s="16"/>
-      <c r="F18" s="8"/>
+      <c r="E18" s="14"/>
+      <c r="F18" s="6"/>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A19" s="3">
+      <c r="A19" s="2">
         <v>18</v>
       </c>
-      <c r="B19" s="11">
+      <c r="B19" s="9">
         <v>1173963052</v>
       </c>
-      <c r="C19" s="1" t="s">
+      <c r="C19" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="D19" s="15" t="s">
-        <v>44</v>
-      </c>
-      <c r="E19" s="16"/>
-      <c r="F19" s="8"/>
+      <c r="D19" s="14"/>
+      <c r="E19" s="14"/>
+      <c r="F19" s="6"/>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A20" s="3">
+      <c r="A20" s="2">
         <v>19</v>
       </c>
-      <c r="B20" s="11">
+      <c r="B20" s="9">
         <v>1173963053</v>
       </c>
-      <c r="C20" s="1" t="s">
+      <c r="C20" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="D20" s="16"/>
-      <c r="E20" s="16"/>
-      <c r="F20" s="8"/>
+      <c r="D20" s="14"/>
+      <c r="E20" s="14"/>
+      <c r="F20" s="6"/>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A21" s="3">
+      <c r="A21" s="2">
         <v>20</v>
       </c>
-      <c r="B21" s="11">
+      <c r="B21" s="9">
         <v>1173963054</v>
       </c>
-      <c r="C21" s="1" t="s">
+      <c r="C21" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="D21" s="16"/>
-      <c r="E21" s="16"/>
-      <c r="F21" s="8"/>
+      <c r="D21" s="14"/>
+      <c r="E21" s="14"/>
+      <c r="F21" s="6"/>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A22" s="3">
+      <c r="A22" s="2">
         <v>21</v>
       </c>
-      <c r="B22" s="11">
+      <c r="B22" s="9">
         <v>1173963055</v>
       </c>
-      <c r="C22" s="1" t="s">
+      <c r="C22" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="D22" s="16"/>
-      <c r="E22" s="16"/>
-      <c r="F22" s="8"/>
+      <c r="D22" s="14"/>
+      <c r="E22" s="14"/>
+      <c r="F22" s="6"/>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A23" s="5">
+      <c r="A23" s="4">
         <v>22</v>
       </c>
-      <c r="B23" s="6">
+      <c r="B23" s="5">
         <v>1173963056</v>
       </c>
-      <c r="C23" s="6" t="s">
+      <c r="C23" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="D23" s="16"/>
-      <c r="E23" s="16"/>
-      <c r="F23" s="8" t="s">
+      <c r="D23" s="14"/>
+      <c r="E23" s="14"/>
+      <c r="F23" s="6" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24" s="2">
+        <v>23</v>
+      </c>
+      <c r="B24" s="9">
+        <v>1173963057</v>
+      </c>
+      <c r="C24" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="D24" s="14"/>
+      <c r="E24" s="14"/>
+      <c r="F24" s="6"/>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A25" s="2">
+        <v>24</v>
+      </c>
+      <c r="B25" s="9">
+        <v>1173963058</v>
+      </c>
+      <c r="C25" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="D25" s="14"/>
+      <c r="E25" s="14"/>
+      <c r="F25" s="6"/>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A26" s="2">
+        <v>25</v>
+      </c>
+      <c r="B26" s="9">
+        <v>1173963059</v>
+      </c>
+      <c r="C26" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="D26" s="14"/>
+      <c r="E26" s="14"/>
+      <c r="F26" s="6"/>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A27" s="2">
+        <v>26</v>
+      </c>
+      <c r="B27" s="9">
+        <v>1173963060</v>
+      </c>
+      <c r="C27" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="D27" s="14"/>
+      <c r="E27" s="14"/>
+      <c r="F27" s="6"/>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A28" s="7">
+        <v>27</v>
+      </c>
+      <c r="B28" s="8">
+        <v>1173963061</v>
+      </c>
+      <c r="C28" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="D28" s="14"/>
+      <c r="E28" s="14"/>
+      <c r="F28" s="6" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A29" s="2">
+        <v>28</v>
+      </c>
+      <c r="B29" s="9">
+        <v>1173963062</v>
+      </c>
+      <c r="C29" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="D29" s="14"/>
+      <c r="E29" s="14"/>
+      <c r="F29" s="6"/>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A30" s="2">
+        <v>29</v>
+      </c>
+      <c r="B30" s="9">
+        <v>1173963063</v>
+      </c>
+      <c r="C30" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="D30" s="14"/>
+      <c r="E30" s="14"/>
+      <c r="F30" s="6"/>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A31" s="2">
+        <v>30</v>
+      </c>
+      <c r="B31" s="9">
+        <v>1173963064</v>
+      </c>
+      <c r="C31" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="D31" s="14"/>
+      <c r="E31" s="14"/>
+      <c r="F31" s="6"/>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A32" s="4">
+        <v>31</v>
+      </c>
+      <c r="B32" s="5">
+        <v>1173963065</v>
+      </c>
+      <c r="C32" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="D32" s="14"/>
+      <c r="E32" s="14"/>
+      <c r="F32" s="6" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A24" s="3">
-        <v>23</v>
-      </c>
-      <c r="B24" s="11">
-        <v>1173963057</v>
-      </c>
-      <c r="C24" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="D24" s="16"/>
-      <c r="E24" s="16"/>
-      <c r="F24" s="8"/>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A25" s="3">
-        <v>24</v>
-      </c>
-      <c r="B25" s="11">
-        <v>1173963058</v>
-      </c>
-      <c r="C25" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D25" s="16"/>
-      <c r="E25" s="16"/>
-      <c r="F25" s="8"/>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A26" s="3">
-        <v>25</v>
-      </c>
-      <c r="B26" s="11">
-        <v>1173963059</v>
-      </c>
-      <c r="C26" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="D26" s="16"/>
-      <c r="E26" s="16"/>
-      <c r="F26" s="8"/>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A27" s="3">
-        <v>26</v>
-      </c>
-      <c r="B27" s="11">
-        <v>1173963060</v>
-      </c>
-      <c r="C27" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="D27" s="16"/>
-      <c r="E27" s="16"/>
-      <c r="F27" s="8"/>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A28" s="9">
-        <v>27</v>
-      </c>
-      <c r="B28" s="10">
-        <v>1173963061</v>
-      </c>
-      <c r="C28" s="10" t="s">
-        <v>29</v>
-      </c>
-      <c r="D28" s="16"/>
-      <c r="E28" s="16"/>
-      <c r="F28" s="8" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A29" s="3">
-        <v>28</v>
-      </c>
-      <c r="B29" s="11">
-        <v>1173963062</v>
-      </c>
-      <c r="C29" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="D29" s="16"/>
-      <c r="E29" s="16"/>
-      <c r="F29" s="8"/>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A30" s="3">
-        <v>29</v>
-      </c>
-      <c r="B30" s="11">
-        <v>1173963063</v>
-      </c>
-      <c r="C30" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="D30" s="16"/>
-      <c r="E30" s="16"/>
-      <c r="F30" s="8"/>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A31" s="3">
-        <v>30</v>
-      </c>
-      <c r="B31" s="11">
-        <v>1173963064</v>
-      </c>
-      <c r="C31" s="1" t="s">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A33" s="2">
         <v>32</v>
       </c>
-      <c r="D31" s="16"/>
-      <c r="E31" s="16"/>
-      <c r="F31" s="8"/>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A32" s="5">
-        <v>31</v>
-      </c>
-      <c r="B32" s="6">
-        <v>1173963065</v>
-      </c>
-      <c r="C32" s="6" t="s">
+      <c r="B33" s="9">
+        <v>1173963066</v>
+      </c>
+      <c r="C33" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="D33" s="14"/>
+      <c r="E33" s="14"/>
+      <c r="F33" s="6"/>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A34" s="2">
         <v>33</v>
       </c>
-      <c r="D32" s="16"/>
-      <c r="E32" s="16"/>
-      <c r="F32" s="8" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A33" s="3">
-        <v>32</v>
-      </c>
-      <c r="B33" s="11">
-        <v>1173963066</v>
-      </c>
-      <c r="C33" s="1" t="s">
+      <c r="B34" s="9">
+        <v>1173963067</v>
+      </c>
+      <c r="C34" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="D34" s="14"/>
+      <c r="E34" s="14"/>
+      <c r="F34" s="6"/>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A35" s="2">
         <v>34</v>
       </c>
-      <c r="D33" s="16"/>
-      <c r="E33" s="16"/>
-      <c r="F33" s="8"/>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A34" s="3">
-        <v>33</v>
-      </c>
-      <c r="B34" s="11">
-        <v>1173963067</v>
-      </c>
-      <c r="C34" s="1" t="s">
+      <c r="B35" s="9">
+        <v>1170534788</v>
+      </c>
+      <c r="C35" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="D35" s="14"/>
+      <c r="E35" s="14"/>
+      <c r="F35" s="6"/>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A36" s="2">
         <v>35</v>
       </c>
-      <c r="D34" s="16"/>
-      <c r="E34" s="16"/>
-      <c r="F34" s="8"/>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A35" s="3">
-        <v>34</v>
-      </c>
-      <c r="B35" s="11">
-        <v>1170534788</v>
-      </c>
-      <c r="C35" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="D35" s="16"/>
-      <c r="E35" s="16"/>
-      <c r="F35" s="8"/>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A36" s="3">
-        <v>35</v>
-      </c>
-      <c r="B36" s="11">
+      <c r="B36" s="9">
         <v>1170534789</v>
       </c>
-      <c r="C36" s="1" t="s">
+      <c r="C36" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="D36" s="17"/>
-      <c r="E36" s="17"/>
-      <c r="F36" s="8"/>
+      <c r="D36" s="15"/>
+      <c r="E36" s="15"/>
+      <c r="F36" s="6"/>
     </row>
   </sheetData>
   <mergeCells count="7">
@@ -1235,8 +1237,8 @@
     <mergeCell ref="E7:E36"/>
     <mergeCell ref="D7:D10"/>
     <mergeCell ref="D11:D14"/>
-    <mergeCell ref="D15:D18"/>
-    <mergeCell ref="D19:D36"/>
+    <mergeCell ref="D15:D36"/>
+    <mergeCell ref="D5:D6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/5. Other/Danh sách số SIM BH-SX/SIM_Test BH-SX.xlsx
+++ b/5. Other/Danh sách số SIM BH-SX/SIM_Test BH-SX.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VNET\5. Other\Danh sách số SIM BH-SX\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB7F216F-19E8-4CB5-A87F-CD97144C120A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{524488F9-96AD-40EB-934C-C1BD3D873439}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{68255EAF-D8EA-4C2C-BCF7-C24A5FBA6E37}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="51">
   <si>
     <t>Seri</t>
   </si>
@@ -176,6 +176,9 @@
   </si>
   <si>
     <t>SIM lỗi, mất phôi</t>
+  </si>
+  <si>
+    <t>Phôi nhựa lỗi lắp sang phôi mobi: 8401210650168374</t>
   </si>
 </sst>
 </file>
@@ -344,6 +347,12 @@
     <xf numFmtId="49" fontId="4" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="3" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -363,12 +372,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -697,22 +700,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="17" t="s">
+      <c r="A1" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="B1" s="17" t="s">
+      <c r="B1" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="17" t="s">
+      <c r="C1" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="17" t="s">
+      <c r="D1" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="17" t="s">
+      <c r="E1" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="F1" s="18" t="s">
+      <c r="F1" s="11" t="s">
         <v>45</v>
       </c>
     </row>
@@ -729,7 +732,7 @@
       <c r="D2" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="E2" s="10" t="s">
+      <c r="E2" s="12" t="s">
         <v>40</v>
       </c>
       <c r="F2" s="6"/>
@@ -744,10 +747,10 @@
       <c r="C3" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D3" s="11" t="s">
+      <c r="D3" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="E3" s="10"/>
+      <c r="E3" s="12"/>
       <c r="F3" s="6"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -760,8 +763,8 @@
       <c r="C4" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D4" s="12"/>
-      <c r="E4" s="10"/>
+      <c r="D4" s="14"/>
+      <c r="E4" s="12"/>
       <c r="F4" s="6"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
@@ -774,10 +777,10 @@
       <c r="C5" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D5" s="13" t="s">
+      <c r="D5" s="15" t="s">
         <v>43</v>
       </c>
-      <c r="E5" s="10"/>
+      <c r="E5" s="12"/>
       <c r="F5" s="6"/>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -790,8 +793,8 @@
       <c r="C6" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="D6" s="15"/>
-      <c r="E6" s="10"/>
+      <c r="D6" s="17"/>
+      <c r="E6" s="12"/>
       <c r="F6" s="6"/>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -804,10 +807,10 @@
       <c r="C7" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="D7" s="11" t="s">
+      <c r="D7" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="E7" s="13" t="s">
+      <c r="E7" s="15" t="s">
         <v>44</v>
       </c>
       <c r="F7" s="6"/>
@@ -822,8 +825,8 @@
       <c r="C8" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D8" s="16"/>
-      <c r="E8" s="14"/>
+      <c r="D8" s="18"/>
+      <c r="E8" s="16"/>
       <c r="F8" s="6" t="s">
         <v>47</v>
       </c>
@@ -838,9 +841,11 @@
       <c r="C9" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D9" s="16"/>
-      <c r="E9" s="14"/>
-      <c r="F9" s="6"/>
+      <c r="D9" s="18"/>
+      <c r="E9" s="16"/>
+      <c r="F9" s="6" t="s">
+        <v>50</v>
+      </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="2">
@@ -852,8 +857,8 @@
       <c r="C10" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D10" s="12"/>
-      <c r="E10" s="14"/>
+      <c r="D10" s="14"/>
+      <c r="E10" s="16"/>
       <c r="F10" s="6"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
@@ -866,10 +871,10 @@
       <c r="C11" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D11" s="11" t="s">
+      <c r="D11" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="E11" s="14"/>
+      <c r="E11" s="16"/>
       <c r="F11" s="6"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
@@ -882,8 +887,8 @@
       <c r="C12" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D12" s="16"/>
-      <c r="E12" s="14"/>
+      <c r="D12" s="18"/>
+      <c r="E12" s="16"/>
       <c r="F12" s="6"/>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
@@ -896,8 +901,8 @@
       <c r="C13" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="D13" s="16"/>
-      <c r="E13" s="14"/>
+      <c r="D13" s="18"/>
+      <c r="E13" s="16"/>
       <c r="F13" s="6"/>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
@@ -910,8 +915,8 @@
       <c r="C14" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D14" s="12"/>
-      <c r="E14" s="14"/>
+      <c r="D14" s="14"/>
+      <c r="E14" s="16"/>
       <c r="F14" s="6"/>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
@@ -924,10 +929,10 @@
       <c r="C15" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D15" s="13" t="s">
+      <c r="D15" s="15" t="s">
         <v>43</v>
       </c>
-      <c r="E15" s="14"/>
+      <c r="E15" s="16"/>
       <c r="F15" s="6"/>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
@@ -940,8 +945,8 @@
       <c r="C16" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D16" s="14"/>
-      <c r="E16" s="14"/>
+      <c r="D16" s="16"/>
+      <c r="E16" s="16"/>
       <c r="F16" s="6"/>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
@@ -954,8 +959,8 @@
       <c r="C17" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D17" s="14"/>
-      <c r="E17" s="14"/>
+      <c r="D17" s="16"/>
+      <c r="E17" s="16"/>
       <c r="F17" s="6"/>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
@@ -968,8 +973,8 @@
       <c r="C18" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D18" s="14"/>
-      <c r="E18" s="14"/>
+      <c r="D18" s="16"/>
+      <c r="E18" s="16"/>
       <c r="F18" s="6"/>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
@@ -982,8 +987,8 @@
       <c r="C19" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="D19" s="14"/>
-      <c r="E19" s="14"/>
+      <c r="D19" s="16"/>
+      <c r="E19" s="16"/>
       <c r="F19" s="6"/>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
@@ -996,8 +1001,8 @@
       <c r="C20" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="D20" s="14"/>
-      <c r="E20" s="14"/>
+      <c r="D20" s="16"/>
+      <c r="E20" s="16"/>
       <c r="F20" s="6"/>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
@@ -1010,8 +1015,8 @@
       <c r="C21" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="D21" s="14"/>
-      <c r="E21" s="14"/>
+      <c r="D21" s="16"/>
+      <c r="E21" s="16"/>
       <c r="F21" s="6"/>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
@@ -1024,8 +1029,8 @@
       <c r="C22" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="D22" s="14"/>
-      <c r="E22" s="14"/>
+      <c r="D22" s="16"/>
+      <c r="E22" s="16"/>
       <c r="F22" s="6"/>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
@@ -1038,8 +1043,8 @@
       <c r="C23" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="D23" s="14"/>
-      <c r="E23" s="14"/>
+      <c r="D23" s="16"/>
+      <c r="E23" s="16"/>
       <c r="F23" s="6" t="s">
         <v>46</v>
       </c>
@@ -1054,8 +1059,8 @@
       <c r="C24" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="D24" s="14"/>
-      <c r="E24" s="14"/>
+      <c r="D24" s="16"/>
+      <c r="E24" s="16"/>
       <c r="F24" s="6"/>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
@@ -1068,8 +1073,8 @@
       <c r="C25" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="D25" s="14"/>
-      <c r="E25" s="14"/>
+      <c r="D25" s="16"/>
+      <c r="E25" s="16"/>
       <c r="F25" s="6"/>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
@@ -1082,8 +1087,8 @@
       <c r="C26" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="D26" s="14"/>
-      <c r="E26" s="14"/>
+      <c r="D26" s="16"/>
+      <c r="E26" s="16"/>
       <c r="F26" s="6"/>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
@@ -1096,8 +1101,8 @@
       <c r="C27" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="D27" s="14"/>
-      <c r="E27" s="14"/>
+      <c r="D27" s="16"/>
+      <c r="E27" s="16"/>
       <c r="F27" s="6"/>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
@@ -1110,8 +1115,8 @@
       <c r="C28" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="D28" s="14"/>
-      <c r="E28" s="14"/>
+      <c r="D28" s="16"/>
+      <c r="E28" s="16"/>
       <c r="F28" s="6" t="s">
         <v>49</v>
       </c>
@@ -1126,8 +1131,8 @@
       <c r="C29" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="D29" s="14"/>
-      <c r="E29" s="14"/>
+      <c r="D29" s="16"/>
+      <c r="E29" s="16"/>
       <c r="F29" s="6"/>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
@@ -1140,8 +1145,8 @@
       <c r="C30" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="D30" s="14"/>
-      <c r="E30" s="14"/>
+      <c r="D30" s="16"/>
+      <c r="E30" s="16"/>
       <c r="F30" s="6"/>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
@@ -1154,8 +1159,8 @@
       <c r="C31" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="D31" s="14"/>
-      <c r="E31" s="14"/>
+      <c r="D31" s="16"/>
+      <c r="E31" s="16"/>
       <c r="F31" s="6"/>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
@@ -1168,8 +1173,8 @@
       <c r="C32" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="D32" s="14"/>
-      <c r="E32" s="14"/>
+      <c r="D32" s="16"/>
+      <c r="E32" s="16"/>
       <c r="F32" s="6" t="s">
         <v>48</v>
       </c>
@@ -1184,8 +1189,8 @@
       <c r="C33" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="D33" s="14"/>
-      <c r="E33" s="14"/>
+      <c r="D33" s="16"/>
+      <c r="E33" s="16"/>
       <c r="F33" s="6"/>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
@@ -1198,8 +1203,8 @@
       <c r="C34" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="D34" s="14"/>
-      <c r="E34" s="14"/>
+      <c r="D34" s="16"/>
+      <c r="E34" s="16"/>
       <c r="F34" s="6"/>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
@@ -1212,8 +1217,8 @@
       <c r="C35" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="D35" s="14"/>
-      <c r="E35" s="14"/>
+      <c r="D35" s="16"/>
+      <c r="E35" s="16"/>
       <c r="F35" s="6"/>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
@@ -1226,8 +1231,8 @@
       <c r="C36" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="D36" s="15"/>
-      <c r="E36" s="15"/>
+      <c r="D36" s="17"/>
+      <c r="E36" s="17"/>
       <c r="F36" s="6"/>
     </row>
   </sheetData>

--- a/5. Other/Danh sách số SIM BH-SX/SIM_Test BH-SX.xlsx
+++ b/5. Other/Danh sách số SIM BH-SX/SIM_Test BH-SX.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VNET\5. Other\Danh sách số SIM BH-SX\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{524488F9-96AD-40EB-934C-C1BD3D873439}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9133DBA6-E69B-4BE2-832F-3ED76C806D28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{68255EAF-D8EA-4C2C-BCF7-C24A5FBA6E37}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="52">
   <si>
     <t>Seri</t>
   </si>
@@ -179,6 +179,9 @@
   </si>
   <si>
     <t>Phôi nhựa lỗi lắp sang phôi mobi: 8401210650168374</t>
+  </si>
+  <si>
+    <t>SIM lỗi phôi</t>
   </si>
 </sst>
 </file>
@@ -322,7 +325,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -372,6 +375,12 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -720,22 +729,24 @@
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="2">
+      <c r="A2" s="7">
         <v>1</v>
       </c>
-      <c r="B2" s="1">
+      <c r="B2" s="19">
         <v>1174221624</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" s="19" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="20" t="s">
         <v>41</v>
       </c>
       <c r="E2" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="F2" s="6"/>
+      <c r="F2" s="6" t="s">
+        <v>51</v>
+      </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="2">
@@ -819,10 +830,10 @@
       <c r="A8" s="2">
         <v>7</v>
       </c>
-      <c r="B8" s="1">
+      <c r="B8" s="8">
         <v>1173963041</v>
       </c>
-      <c r="C8" s="1" t="s">
+      <c r="C8" s="8" t="s">
         <v>9</v>
       </c>
       <c r="D8" s="18"/>

--- a/5. Other/Danh sách số SIM BH-SX/SIM_Test BH-SX.xlsx
+++ b/5. Other/Danh sách số SIM BH-SX/SIM_Test BH-SX.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VNET\5. Other\Danh sách số SIM BH-SX\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9133DBA6-E69B-4BE2-832F-3ED76C806D28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91D41EF2-71F6-42A6-A546-8049508F6BB6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{68255EAF-D8EA-4C2C-BCF7-C24A5FBA6E37}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="59">
   <si>
     <t>Seri</t>
   </si>
@@ -182,6 +182,27 @@
   </si>
   <si>
     <t>SIM lỗi phôi</t>
+  </si>
+  <si>
+    <t>8984048000969492510</t>
+  </si>
+  <si>
+    <t>8984048000969492511</t>
+  </si>
+  <si>
+    <t>8984048000969492512</t>
+  </si>
+  <si>
+    <t>Test VNSH03</t>
+  </si>
+  <si>
+    <t>01699555434</t>
+  </si>
+  <si>
+    <t>01699555435</t>
+  </si>
+  <si>
+    <t>01699555418</t>
   </si>
 </sst>
 </file>
@@ -325,7 +346,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -353,19 +374,13 @@
     <xf numFmtId="49" fontId="3" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="49" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -374,14 +389,24 @@
     <xf numFmtId="49" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -697,11 +722,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{69ED331E-3E24-49D9-A8FD-C7C548CF9C48}">
-  <dimension ref="A1:F36"/>
+  <dimension ref="A1:F39"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5.140625" style="3" customWidth="1"/>
-    <col min="2" max="2" width="15.85546875" style="3" customWidth="1"/>
+    <col min="2" max="2" width="24.28515625" style="3" customWidth="1"/>
     <col min="3" max="3" width="18" style="3" customWidth="1"/>
     <col min="4" max="4" width="18.5703125" style="3" customWidth="1"/>
     <col min="5" max="5" width="14.7109375" style="3" customWidth="1"/>
@@ -724,7 +749,7 @@
       <c r="E1" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="F1" s="11" t="s">
+      <c r="F1" s="10" t="s">
         <v>45</v>
       </c>
     </row>
@@ -732,13 +757,13 @@
       <c r="A2" s="7">
         <v>1</v>
       </c>
-      <c r="B2" s="19">
+      <c r="B2" s="11">
         <v>1174221624</v>
       </c>
-      <c r="C2" s="19" t="s">
+      <c r="C2" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="20" t="s">
+      <c r="D2" s="2" t="s">
         <v>41</v>
       </c>
       <c r="E2" s="12" t="s">
@@ -758,7 +783,7 @@
       <c r="C3" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D3" s="13" t="s">
+      <c r="D3" s="16" t="s">
         <v>42</v>
       </c>
       <c r="E3" s="12"/>
@@ -774,7 +799,7 @@
       <c r="C4" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D4" s="14"/>
+      <c r="D4" s="16"/>
       <c r="E4" s="12"/>
       <c r="F4" s="6"/>
     </row>
@@ -788,7 +813,7 @@
       <c r="C5" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D5" s="15" t="s">
+      <c r="D5" s="17" t="s">
         <v>43</v>
       </c>
       <c r="E5" s="12"/>
@@ -818,10 +843,10 @@
       <c r="C7" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="D7" s="13" t="s">
+      <c r="D7" s="16" t="s">
         <v>41</v>
       </c>
-      <c r="E7" s="15" t="s">
+      <c r="E7" s="13" t="s">
         <v>44</v>
       </c>
       <c r="F7" s="6"/>
@@ -836,8 +861,8 @@
       <c r="C8" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="D8" s="18"/>
-      <c r="E8" s="16"/>
+      <c r="D8" s="16"/>
+      <c r="E8" s="14"/>
       <c r="F8" s="6" t="s">
         <v>47</v>
       </c>
@@ -852,8 +877,8 @@
       <c r="C9" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D9" s="18"/>
-      <c r="E9" s="16"/>
+      <c r="D9" s="16"/>
+      <c r="E9" s="14"/>
       <c r="F9" s="6" t="s">
         <v>50</v>
       </c>
@@ -868,8 +893,8 @@
       <c r="C10" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D10" s="14"/>
-      <c r="E10" s="16"/>
+      <c r="D10" s="16"/>
+      <c r="E10" s="14"/>
       <c r="F10" s="6"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
@@ -882,10 +907,10 @@
       <c r="C11" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D11" s="13" t="s">
+      <c r="D11" s="16" t="s">
         <v>42</v>
       </c>
-      <c r="E11" s="16"/>
+      <c r="E11" s="14"/>
       <c r="F11" s="6"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
@@ -898,8 +923,8 @@
       <c r="C12" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D12" s="18"/>
-      <c r="E12" s="16"/>
+      <c r="D12" s="16"/>
+      <c r="E12" s="14"/>
       <c r="F12" s="6"/>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
@@ -912,8 +937,8 @@
       <c r="C13" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="D13" s="18"/>
-      <c r="E13" s="16"/>
+      <c r="D13" s="16"/>
+      <c r="E13" s="14"/>
       <c r="F13" s="6"/>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
@@ -926,8 +951,8 @@
       <c r="C14" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D14" s="14"/>
-      <c r="E14" s="16"/>
+      <c r="D14" s="16"/>
+      <c r="E14" s="14"/>
       <c r="F14" s="6"/>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
@@ -940,10 +965,10 @@
       <c r="C15" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D15" s="15" t="s">
+      <c r="D15" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="E15" s="16"/>
+      <c r="E15" s="14"/>
       <c r="F15" s="6"/>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
@@ -956,8 +981,8 @@
       <c r="C16" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D16" s="16"/>
-      <c r="E16" s="16"/>
+      <c r="D16" s="14"/>
+      <c r="E16" s="14"/>
       <c r="F16" s="6"/>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
@@ -970,8 +995,8 @@
       <c r="C17" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D17" s="16"/>
-      <c r="E17" s="16"/>
+      <c r="D17" s="14"/>
+      <c r="E17" s="14"/>
       <c r="F17" s="6"/>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
@@ -984,8 +1009,8 @@
       <c r="C18" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D18" s="16"/>
-      <c r="E18" s="16"/>
+      <c r="D18" s="14"/>
+      <c r="E18" s="14"/>
       <c r="F18" s="6"/>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
@@ -998,8 +1023,8 @@
       <c r="C19" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="D19" s="16"/>
-      <c r="E19" s="16"/>
+      <c r="D19" s="14"/>
+      <c r="E19" s="14"/>
       <c r="F19" s="6"/>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
@@ -1012,8 +1037,8 @@
       <c r="C20" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="D20" s="16"/>
-      <c r="E20" s="16"/>
+      <c r="D20" s="14"/>
+      <c r="E20" s="14"/>
       <c r="F20" s="6"/>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
@@ -1026,8 +1051,8 @@
       <c r="C21" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="D21" s="16"/>
-      <c r="E21" s="16"/>
+      <c r="D21" s="14"/>
+      <c r="E21" s="14"/>
       <c r="F21" s="6"/>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
@@ -1040,8 +1065,8 @@
       <c r="C22" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="D22" s="16"/>
-      <c r="E22" s="16"/>
+      <c r="D22" s="14"/>
+      <c r="E22" s="14"/>
       <c r="F22" s="6"/>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
@@ -1054,8 +1079,8 @@
       <c r="C23" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="D23" s="16"/>
-      <c r="E23" s="16"/>
+      <c r="D23" s="14"/>
+      <c r="E23" s="14"/>
       <c r="F23" s="6" t="s">
         <v>46</v>
       </c>
@@ -1070,8 +1095,8 @@
       <c r="C24" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="D24" s="16"/>
-      <c r="E24" s="16"/>
+      <c r="D24" s="14"/>
+      <c r="E24" s="14"/>
       <c r="F24" s="6"/>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
@@ -1084,8 +1109,8 @@
       <c r="C25" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="D25" s="16"/>
-      <c r="E25" s="16"/>
+      <c r="D25" s="14"/>
+      <c r="E25" s="14"/>
       <c r="F25" s="6"/>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
@@ -1098,8 +1123,8 @@
       <c r="C26" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="D26" s="16"/>
-      <c r="E26" s="16"/>
+      <c r="D26" s="14"/>
+      <c r="E26" s="14"/>
       <c r="F26" s="6"/>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
@@ -1112,8 +1137,8 @@
       <c r="C27" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="D27" s="16"/>
-      <c r="E27" s="16"/>
+      <c r="D27" s="14"/>
+      <c r="E27" s="14"/>
       <c r="F27" s="6"/>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
@@ -1126,8 +1151,8 @@
       <c r="C28" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="D28" s="16"/>
-      <c r="E28" s="16"/>
+      <c r="D28" s="14"/>
+      <c r="E28" s="14"/>
       <c r="F28" s="6" t="s">
         <v>49</v>
       </c>
@@ -1142,8 +1167,8 @@
       <c r="C29" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="D29" s="16"/>
-      <c r="E29" s="16"/>
+      <c r="D29" s="14"/>
+      <c r="E29" s="14"/>
       <c r="F29" s="6"/>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
@@ -1156,8 +1181,8 @@
       <c r="C30" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="D30" s="16"/>
-      <c r="E30" s="16"/>
+      <c r="D30" s="14"/>
+      <c r="E30" s="14"/>
       <c r="F30" s="6"/>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
@@ -1170,8 +1195,8 @@
       <c r="C31" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="D31" s="16"/>
-      <c r="E31" s="16"/>
+      <c r="D31" s="14"/>
+      <c r="E31" s="14"/>
       <c r="F31" s="6"/>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
@@ -1184,8 +1209,8 @@
       <c r="C32" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="D32" s="16"/>
-      <c r="E32" s="16"/>
+      <c r="D32" s="14"/>
+      <c r="E32" s="14"/>
       <c r="F32" s="6" t="s">
         <v>48</v>
       </c>
@@ -1200,8 +1225,8 @@
       <c r="C33" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="D33" s="16"/>
-      <c r="E33" s="16"/>
+      <c r="D33" s="14"/>
+      <c r="E33" s="14"/>
       <c r="F33" s="6"/>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
@@ -1214,8 +1239,8 @@
       <c r="C34" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="D34" s="16"/>
-      <c r="E34" s="16"/>
+      <c r="D34" s="14"/>
+      <c r="E34" s="14"/>
       <c r="F34" s="6"/>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
@@ -1228,8 +1253,8 @@
       <c r="C35" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="D35" s="16"/>
-      <c r="E35" s="16"/>
+      <c r="D35" s="14"/>
+      <c r="E35" s="14"/>
       <c r="F35" s="6"/>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
@@ -1242,9 +1267,57 @@
       <c r="C36" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="D36" s="17"/>
-      <c r="E36" s="17"/>
+      <c r="D36" s="14"/>
+      <c r="E36" s="14"/>
       <c r="F36" s="6"/>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A37" s="2">
+        <v>36</v>
+      </c>
+      <c r="B37" s="19" t="s">
+        <v>52</v>
+      </c>
+      <c r="C37" s="20" t="s">
+        <v>56</v>
+      </c>
+      <c r="D37" s="14"/>
+      <c r="E37" s="22" t="s">
+        <v>55</v>
+      </c>
+      <c r="F37" s="18"/>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A38" s="2">
+        <v>37</v>
+      </c>
+      <c r="B38" s="21" t="s">
+        <v>53</v>
+      </c>
+      <c r="C38" s="20" t="s">
+        <v>57</v>
+      </c>
+      <c r="D38" s="14"/>
+      <c r="E38" s="22" t="s">
+        <v>55</v>
+      </c>
+      <c r="F38" s="18"/>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A39" s="2">
+        <v>38</v>
+      </c>
+      <c r="B39" s="21" t="s">
+        <v>54</v>
+      </c>
+      <c r="C39" s="20" t="s">
+        <v>58</v>
+      </c>
+      <c r="D39" s="15"/>
+      <c r="E39" s="22" t="s">
+        <v>55</v>
+      </c>
+      <c r="F39" s="18"/>
     </row>
   </sheetData>
   <mergeCells count="7">
@@ -1253,8 +1326,8 @@
     <mergeCell ref="E7:E36"/>
     <mergeCell ref="D7:D10"/>
     <mergeCell ref="D11:D14"/>
-    <mergeCell ref="D15:D36"/>
     <mergeCell ref="D5:D6"/>
+    <mergeCell ref="D15:D39"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/5. Other/Danh sách số SIM BH-SX/SIM_Test BH-SX.xlsx
+++ b/5. Other/Danh sách số SIM BH-SX/SIM_Test BH-SX.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VNET\5. Other\Danh sách số SIM BH-SX\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91D41EF2-71F6-42A6-A546-8049508F6BB6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82C19206-11DD-40B8-8D3F-5EA7D23EFCF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{68255EAF-D8EA-4C2C-BCF7-C24A5FBA6E37}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{68255EAF-D8EA-4C2C-BCF7-C24A5FBA6E37}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="59">
   <si>
     <t>Seri</t>
   </si>
@@ -377,24 +377,6 @@
     <xf numFmtId="49" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -407,6 +389,24 @@
     </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -426,9 +426,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -466,7 +466,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -572,7 +572,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -714,7 +714,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -766,7 +766,7 @@
       <c r="D2" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="E2" s="12" t="s">
+      <c r="E2" s="17" t="s">
         <v>40</v>
       </c>
       <c r="F2" s="6" t="s">
@@ -774,20 +774,22 @@
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="2">
+      <c r="A3" s="7">
         <v>2</v>
       </c>
-      <c r="B3" s="1">
+      <c r="B3" s="11">
         <v>1174221625</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="C3" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="D3" s="16" t="s">
+      <c r="D3" s="18" t="s">
         <v>42</v>
       </c>
-      <c r="E3" s="12"/>
-      <c r="F3" s="6"/>
+      <c r="E3" s="17"/>
+      <c r="F3" s="6" t="s">
+        <v>46</v>
+      </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="2">
@@ -799,8 +801,8 @@
       <c r="C4" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D4" s="16"/>
-      <c r="E4" s="12"/>
+      <c r="D4" s="18"/>
+      <c r="E4" s="17"/>
       <c r="F4" s="6"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
@@ -813,10 +815,10 @@
       <c r="C5" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D5" s="17" t="s">
+      <c r="D5" s="21" t="s">
         <v>43</v>
       </c>
-      <c r="E5" s="12"/>
+      <c r="E5" s="17"/>
       <c r="F5" s="6"/>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -829,8 +831,8 @@
       <c r="C6" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="D6" s="17"/>
-      <c r="E6" s="12"/>
+      <c r="D6" s="21"/>
+      <c r="E6" s="17"/>
       <c r="F6" s="6"/>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -843,16 +845,16 @@
       <c r="C7" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="D7" s="16" t="s">
+      <c r="D7" s="18" t="s">
         <v>41</v>
       </c>
-      <c r="E7" s="13" t="s">
+      <c r="E7" s="19" t="s">
         <v>44</v>
       </c>
       <c r="F7" s="6"/>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="2">
+      <c r="A8" s="7">
         <v>7</v>
       </c>
       <c r="B8" s="8">
@@ -861,8 +863,8 @@
       <c r="C8" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="D8" s="16"/>
-      <c r="E8" s="14"/>
+      <c r="D8" s="18"/>
+      <c r="E8" s="20"/>
       <c r="F8" s="6" t="s">
         <v>47</v>
       </c>
@@ -877,8 +879,8 @@
       <c r="C9" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D9" s="16"/>
-      <c r="E9" s="14"/>
+      <c r="D9" s="18"/>
+      <c r="E9" s="20"/>
       <c r="F9" s="6" t="s">
         <v>50</v>
       </c>
@@ -893,8 +895,8 @@
       <c r="C10" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D10" s="16"/>
-      <c r="E10" s="14"/>
+      <c r="D10" s="18"/>
+      <c r="E10" s="20"/>
       <c r="F10" s="6"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
@@ -907,25 +909,27 @@
       <c r="C11" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D11" s="16" t="s">
+      <c r="D11" s="18" t="s">
         <v>42</v>
       </c>
-      <c r="E11" s="14"/>
+      <c r="E11" s="20"/>
       <c r="F11" s="6"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="2">
+      <c r="A12" s="7">
         <v>11</v>
       </c>
-      <c r="B12" s="1">
+      <c r="B12" s="8">
         <v>1173963045</v>
       </c>
-      <c r="C12" s="1" t="s">
+      <c r="C12" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="D12" s="16"/>
-      <c r="E12" s="14"/>
-      <c r="F12" s="6"/>
+      <c r="D12" s="18"/>
+      <c r="E12" s="20"/>
+      <c r="F12" s="6" t="s">
+        <v>46</v>
+      </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="2">
@@ -937,8 +941,8 @@
       <c r="C13" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="D13" s="16"/>
-      <c r="E13" s="14"/>
+      <c r="D13" s="18"/>
+      <c r="E13" s="20"/>
       <c r="F13" s="6"/>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
@@ -951,8 +955,8 @@
       <c r="C14" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D14" s="16"/>
-      <c r="E14" s="14"/>
+      <c r="D14" s="18"/>
+      <c r="E14" s="20"/>
       <c r="F14" s="6"/>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
@@ -965,10 +969,10 @@
       <c r="C15" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D15" s="13" t="s">
+      <c r="D15" s="19" t="s">
         <v>43</v>
       </c>
-      <c r="E15" s="14"/>
+      <c r="E15" s="20"/>
       <c r="F15" s="6"/>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
@@ -981,8 +985,8 @@
       <c r="C16" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D16" s="14"/>
-      <c r="E16" s="14"/>
+      <c r="D16" s="20"/>
+      <c r="E16" s="20"/>
       <c r="F16" s="6"/>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
@@ -995,8 +999,8 @@
       <c r="C17" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D17" s="14"/>
-      <c r="E17" s="14"/>
+      <c r="D17" s="20"/>
+      <c r="E17" s="20"/>
       <c r="F17" s="6"/>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
@@ -1009,8 +1013,8 @@
       <c r="C18" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D18" s="14"/>
-      <c r="E18" s="14"/>
+      <c r="D18" s="20"/>
+      <c r="E18" s="20"/>
       <c r="F18" s="6"/>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
@@ -1023,8 +1027,8 @@
       <c r="C19" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="D19" s="14"/>
-      <c r="E19" s="14"/>
+      <c r="D19" s="20"/>
+      <c r="E19" s="20"/>
       <c r="F19" s="6"/>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
@@ -1037,8 +1041,8 @@
       <c r="C20" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="D20" s="14"/>
-      <c r="E20" s="14"/>
+      <c r="D20" s="20"/>
+      <c r="E20" s="20"/>
       <c r="F20" s="6"/>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
@@ -1051,8 +1055,8 @@
       <c r="C21" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="D21" s="14"/>
-      <c r="E21" s="14"/>
+      <c r="D21" s="20"/>
+      <c r="E21" s="20"/>
       <c r="F21" s="6"/>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
@@ -1065,8 +1069,8 @@
       <c r="C22" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="D22" s="14"/>
-      <c r="E22" s="14"/>
+      <c r="D22" s="20"/>
+      <c r="E22" s="20"/>
       <c r="F22" s="6"/>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
@@ -1079,8 +1083,8 @@
       <c r="C23" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="D23" s="14"/>
-      <c r="E23" s="14"/>
+      <c r="D23" s="20"/>
+      <c r="E23" s="20"/>
       <c r="F23" s="6" t="s">
         <v>46</v>
       </c>
@@ -1095,8 +1099,8 @@
       <c r="C24" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="D24" s="14"/>
-      <c r="E24" s="14"/>
+      <c r="D24" s="20"/>
+      <c r="E24" s="20"/>
       <c r="F24" s="6"/>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
@@ -1109,8 +1113,8 @@
       <c r="C25" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="D25" s="14"/>
-      <c r="E25" s="14"/>
+      <c r="D25" s="20"/>
+      <c r="E25" s="20"/>
       <c r="F25" s="6"/>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
@@ -1123,8 +1127,8 @@
       <c r="C26" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="D26" s="14"/>
-      <c r="E26" s="14"/>
+      <c r="D26" s="20"/>
+      <c r="E26" s="20"/>
       <c r="F26" s="6"/>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
@@ -1137,8 +1141,8 @@
       <c r="C27" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="D27" s="14"/>
-      <c r="E27" s="14"/>
+      <c r="D27" s="20"/>
+      <c r="E27" s="20"/>
       <c r="F27" s="6"/>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
@@ -1151,8 +1155,8 @@
       <c r="C28" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="D28" s="14"/>
-      <c r="E28" s="14"/>
+      <c r="D28" s="20"/>
+      <c r="E28" s="20"/>
       <c r="F28" s="6" t="s">
         <v>49</v>
       </c>
@@ -1167,8 +1171,8 @@
       <c r="C29" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="D29" s="14"/>
-      <c r="E29" s="14"/>
+      <c r="D29" s="20"/>
+      <c r="E29" s="20"/>
       <c r="F29" s="6"/>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
@@ -1181,8 +1185,8 @@
       <c r="C30" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="D30" s="14"/>
-      <c r="E30" s="14"/>
+      <c r="D30" s="20"/>
+      <c r="E30" s="20"/>
       <c r="F30" s="6"/>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
@@ -1195,8 +1199,8 @@
       <c r="C31" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="D31" s="14"/>
-      <c r="E31" s="14"/>
+      <c r="D31" s="20"/>
+      <c r="E31" s="20"/>
       <c r="F31" s="6"/>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
@@ -1209,8 +1213,8 @@
       <c r="C32" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="D32" s="14"/>
-      <c r="E32" s="14"/>
+      <c r="D32" s="20"/>
+      <c r="E32" s="20"/>
       <c r="F32" s="6" t="s">
         <v>48</v>
       </c>
@@ -1225,8 +1229,8 @@
       <c r="C33" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="D33" s="14"/>
-      <c r="E33" s="14"/>
+      <c r="D33" s="20"/>
+      <c r="E33" s="20"/>
       <c r="F33" s="6"/>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
@@ -1239,8 +1243,8 @@
       <c r="C34" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="D34" s="14"/>
-      <c r="E34" s="14"/>
+      <c r="D34" s="20"/>
+      <c r="E34" s="20"/>
       <c r="F34" s="6"/>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
@@ -1253,8 +1257,8 @@
       <c r="C35" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="D35" s="14"/>
-      <c r="E35" s="14"/>
+      <c r="D35" s="20"/>
+      <c r="E35" s="20"/>
       <c r="F35" s="6"/>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
@@ -1267,57 +1271,57 @@
       <c r="C36" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="D36" s="14"/>
-      <c r="E36" s="14"/>
+      <c r="D36" s="20"/>
+      <c r="E36" s="20"/>
       <c r="F36" s="6"/>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="2">
         <v>36</v>
       </c>
-      <c r="B37" s="19" t="s">
+      <c r="B37" s="13" t="s">
         <v>52</v>
       </c>
-      <c r="C37" s="20" t="s">
+      <c r="C37" s="14" t="s">
         <v>56</v>
       </c>
-      <c r="D37" s="14"/>
-      <c r="E37" s="22" t="s">
+      <c r="D37" s="20"/>
+      <c r="E37" s="16" t="s">
         <v>55</v>
       </c>
-      <c r="F37" s="18"/>
+      <c r="F37" s="12"/>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="2">
         <v>37</v>
       </c>
-      <c r="B38" s="21" t="s">
+      <c r="B38" s="15" t="s">
         <v>53</v>
       </c>
-      <c r="C38" s="20" t="s">
+      <c r="C38" s="14" t="s">
         <v>57</v>
       </c>
-      <c r="D38" s="14"/>
-      <c r="E38" s="22" t="s">
+      <c r="D38" s="20"/>
+      <c r="E38" s="16" t="s">
         <v>55</v>
       </c>
-      <c r="F38" s="18"/>
+      <c r="F38" s="12"/>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="2">
         <v>38</v>
       </c>
-      <c r="B39" s="21" t="s">
+      <c r="B39" s="15" t="s">
         <v>54</v>
       </c>
-      <c r="C39" s="20" t="s">
+      <c r="C39" s="14" t="s">
         <v>58</v>
       </c>
-      <c r="D39" s="15"/>
-      <c r="E39" s="22" t="s">
+      <c r="D39" s="22"/>
+      <c r="E39" s="16" t="s">
         <v>55</v>
       </c>
-      <c r="F39" s="18"/>
+      <c r="F39" s="12"/>
     </row>
   </sheetData>
   <mergeCells count="7">
@@ -1330,5 +1334,6 @@
     <mergeCell ref="D15:D39"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="256" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>
 </file>
--- a/5. Other/Danh sách số SIM BH-SX/SIM_Test BH-SX.xlsx
+++ b/5. Other/Danh sách số SIM BH-SX/SIM_Test BH-SX.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VNET\5. Other\Danh sách số SIM BH-SX\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VNETGPS\VNET\5. Other\Danh sách số SIM BH-SX\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82C19206-11DD-40B8-8D3F-5EA7D23EFCF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DEB68111-A89C-4B37-A08E-15C1E6D9ED15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{68255EAF-D8EA-4C2C-BCF7-C24A5FBA6E37}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{68255EAF-D8EA-4C2C-BCF7-C24A5FBA6E37}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="60">
   <si>
     <t>Seri</t>
   </si>
@@ -203,6 +203,9 @@
   </si>
   <si>
     <t>01699555418</t>
+  </si>
+  <si>
+    <t>cho a thông mượn</t>
   </si>
 </sst>
 </file>
@@ -426,9 +429,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -466,7 +469,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -572,7 +575,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -714,7 +717,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1057,7 +1060,9 @@
       </c>
       <c r="D21" s="20"/>
       <c r="E21" s="20"/>
-      <c r="F21" s="6"/>
+      <c r="F21" s="6" t="s">
+        <v>59</v>
+      </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="2">
@@ -1289,7 +1294,9 @@
       <c r="E37" s="16" t="s">
         <v>55</v>
       </c>
-      <c r="F37" s="12"/>
+      <c r="F37" s="12" t="s">
+        <v>59</v>
+      </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="2">

--- a/5. Other/Danh sách số SIM BH-SX/SIM_Test BH-SX.xlsx
+++ b/5. Other/Danh sách số SIM BH-SX/SIM_Test BH-SX.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VNETGPS\VNET\5. Other\Danh sách số SIM BH-SX\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VNET\5. Other\Danh sách số SIM BH-SX\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DEB68111-A89C-4B37-A08E-15C1E6D9ED15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC80D5A7-F605-41F6-A101-8F16B9E33C19}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{68255EAF-D8EA-4C2C-BCF7-C24A5FBA6E37}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{68255EAF-D8EA-4C2C-BCF7-C24A5FBA6E37}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="62">
   <si>
     <t>Seri</t>
   </si>
@@ -206,6 +206,12 @@
   </si>
   <si>
     <t>cho a thông mượn</t>
+  </si>
+  <si>
+    <t>Tùng đang sử dụng</t>
+  </si>
+  <si>
+    <t>Hậu đang sử dụng</t>
   </si>
 </sst>
 </file>
@@ -1295,7 +1301,7 @@
         <v>55</v>
       </c>
       <c r="F37" s="12" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
@@ -1312,7 +1318,9 @@
       <c r="E38" s="16" t="s">
         <v>55</v>
       </c>
-      <c r="F38" s="12"/>
+      <c r="F38" s="12" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="2">
@@ -1328,7 +1336,9 @@
       <c r="E39" s="16" t="s">
         <v>55</v>
       </c>
-      <c r="F39" s="12"/>
+      <c r="F39" s="12" t="s">
+        <v>59</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="7">
